--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/1500000/Output_0_12.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/1500000/Output_0_12.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>507843.8865985537</v>
+        <v>507846.9793192722</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>925658.2446351895</v>
+        <v>925399.3994514378</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18327269.62422527</v>
+        <v>18327015.93006066</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5571761.79076661</v>
+        <v>5571875.219309997</v>
       </c>
     </row>
     <row r="11">
@@ -691,31 +691,31 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T2" t="n">
         <v>223.0958495641314</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V2" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>230.1769504358686</v>
+        <v>11.19305615617957</v>
       </c>
     </row>
     <row r="3">
@@ -728,25 +728,25 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>145.3912560091964</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0.7465913262578567</v>
@@ -776,19 +776,19 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>34.66067414728066</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -825,13 +825,13 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>17.55829564281238</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -846,13 +846,13 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>44.30348359856715</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -940,10 +940,10 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U5" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V5" t="n">
-        <v>102.2970636939287</v>
+        <v>90.38893773807641</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -965,19 +965,19 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>145.4467082856156</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G6" t="n">
-        <v>34.94701555355315</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H6" t="n">
         <v>112.2354442364965</v>
@@ -1010,16 +1010,16 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1044,13 +1044,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1132,16 +1132,16 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>230.8744955960827</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J8" t="n">
         <v>11.94928935461252</v>
@@ -1165,22 +1165,22 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>90.34777433931619</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1202,19 +1202,19 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>145.3912560091964</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>137.3435171632106</v>
+        <v>80.47961400380896</v>
       </c>
       <c r="H9" t="n">
         <v>112.2354442364965</v>
@@ -1262,13 +1262,13 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="10">
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>17.55829564281238</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>22.26949182588285</v>
@@ -1320,13 +1320,13 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>22.0339917726843</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1414,10 +1414,10 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U11" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V11" t="n">
-        <v>102.2970636939287</v>
+        <v>102.3382270926889</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -1439,10 +1439,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>145.4467082856156</v>
       </c>
       <c r="D12" t="n">
-        <v>20.99531631735417</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E12" t="n">
         <v>157.6450804554009</v>
@@ -1484,10 +1484,10 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1563,7 +1563,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R13" t="n">
-        <v>44.30348359856712</v>
+        <v>44.30348359856715</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1600,13 +1600,13 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F14" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1615,10 +1615,10 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1651,16 +1651,16 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>230.8476210749815</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>145.4467082856156</v>
       </c>
       <c r="D15" t="n">
         <v>147.4450655646388</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>145.3912560091964</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1773,13 +1773,13 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>17.55829564281238</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1794,13 +1794,13 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>44.30348359856715</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1843,16 +1843,16 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>230.8744955960827</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J17" t="n">
         <v>11.94928935461252</v>
@@ -1876,22 +1876,22 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>90.34777433931619</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1973,7 +1973,7 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W18" t="n">
-        <v>3.778505492039412</v>
+        <v>4.580549094716531</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2071,10 +2071,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2113,31 +2113,31 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>190.3453970742849</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="21">
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
         <v>147.4450655646388</v>
@@ -2162,7 +2162,7 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>59.00733081077995</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>8.583694061602047</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -2317,19 +2317,19 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.79691042959408</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I23" t="n">
-        <v>210.4758895704059</v>
+        <v>200.3360962888296</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2374,7 +2374,7 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2387,7 +2387,7 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -2399,10 +2399,10 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2432,25 +2432,25 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>13.11092414077382</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>110.1086200309024</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X24" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
         <v>205.6826957773044</v>
@@ -2463,16 +2463,16 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -2551,10 +2551,10 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2587,19 +2587,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>70.31713328017405</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="27">
@@ -2621,13 +2621,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -2642,7 +2642,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>50.0165318697929</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2675,19 +2675,19 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>189.725925203634</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
         <v>205.6826957773044</v>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -2763,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -2791,16 +2791,16 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>21.15688084966667</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2830,16 +2830,16 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="30">
@@ -2861,10 +2861,10 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>56.17030901074568</v>
       </c>
       <c r="D30" t="n">
-        <v>50.0165318697929</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2915,13 +2915,13 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X30" t="n">
         <v>205.7729852034775</v>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -3031,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3079,13 +3079,13 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X32" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>220.1862512213238</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3095,31 +3095,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>91.00671443664322</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>51.83632157383516</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3146,25 +3146,25 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="34">
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -3237,7 +3237,7 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -3262,13 +3262,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G35" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -3277,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -3298,22 +3298,22 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>9.20759149508296</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -3322,7 +3322,7 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
     </row>
     <row r="36">
@@ -3335,25 +3335,25 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>106.8363232633404</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3380,25 +3380,25 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>29.79900896488251</v>
       </c>
       <c r="S36" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -3426,7 +3426,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -3477,7 +3477,7 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -3493,16 +3493,16 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -3511,10 +3511,10 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3538,16 +3538,16 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>120.8718847689103</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -3556,7 +3556,7 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -3572,13 +3572,13 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>141.3598116963804</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3620,25 +3620,25 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>96.96441691716383</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X39" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3693,19 +3693,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>47.02492433367365</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -3739,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -3775,7 +3775,7 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -3790,13 +3790,13 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>52.41298284430547</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="Y41" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="42">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -3815,7 +3815,7 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3860,22 +3860,22 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>137.2939487453064</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>29.05241763862477</v>
       </c>
     </row>
     <row r="43">
@@ -3939,10 +3939,10 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -3973,19 +3973,19 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>202.2821007854552</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4024,16 +4024,16 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
     </row>
     <row r="45">
@@ -4055,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -4064,10 +4064,10 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>15.33384628346822</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -4091,28 +4091,28 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W45" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>29.79900896488263</v>
       </c>
     </row>
     <row r="46">
@@ -4179,10 +4179,10 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
       </c>
       <c r="W46" t="n">
         <v>0</v>
@@ -4289,76 +4289,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K2" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L2" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M2" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N2" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O2" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P2" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q2" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R2" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S2" t="n">
-        <v>964</v>
+        <v>742.8341567219593</v>
       </c>
       <c r="T2" t="n">
-        <v>738.6506570059279</v>
+        <v>517.4848137278872</v>
       </c>
       <c r="U2" t="n">
-        <v>738.6506570059279</v>
+        <v>274.0360370837871</v>
       </c>
       <c r="V2" t="n">
-        <v>495.2163135715845</v>
+        <v>30.58726043968704</v>
       </c>
       <c r="W2" t="n">
-        <v>495.2163135715845</v>
+        <v>30.58726043968704</v>
       </c>
       <c r="X2" t="n">
-        <v>251.781970137241</v>
+        <v>30.58726043968704</v>
       </c>
       <c r="Y2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="3">
@@ -4368,76 +4368,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>964</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="C3" t="n">
-        <v>817.1401454452562</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D3" t="n">
-        <v>668.2057357840049</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E3" t="n">
-        <v>508.9682807785495</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F3" t="n">
-        <v>362.4337228054344</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G3" t="n">
-        <v>223.7028973880499</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H3" t="n">
-        <v>110.3337617956292</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I3" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J3" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K3" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L3" t="n">
-        <v>234.7819638733197</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M3" t="n">
-        <v>234.7819638733197</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N3" t="n">
-        <v>473.3719638733197</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="O3" t="n">
-        <v>711.9619638733197</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="P3" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S3" t="n">
-        <v>964</v>
+        <v>929.0463735436861</v>
       </c>
       <c r="T3" t="n">
-        <v>964</v>
+        <v>726.8597789024521</v>
       </c>
       <c r="U3" t="n">
-        <v>964</v>
+        <v>498.6361606388412</v>
       </c>
       <c r="V3" t="n">
-        <v>964</v>
+        <v>263.4840524070985</v>
       </c>
       <c r="W3" t="n">
-        <v>964</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="X3" t="n">
-        <v>964</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="Y3" t="n">
-        <v>964</v>
+        <v>20.03527576299844</v>
       </c>
     </row>
     <row r="4">
@@ -4447,76 +4447,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I4" t="n">
-        <v>136.0766383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J4" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K4" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L4" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M4" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N4" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P4" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Q4" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="R4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y4" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="5">
@@ -4526,76 +4526,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="C5" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="D5" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="E5" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="F5" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="G5" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="H5" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="I5" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J5" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K5" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L5" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M5" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N5" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O5" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q5" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R5" t="n">
-        <v>802.5254372164702</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S5" t="n">
-        <v>591.3940537960203</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="T5" t="n">
-        <v>366.0447108019482</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="U5" t="n">
-        <v>122.6103673676048</v>
+        <v>122.6530896684844</v>
       </c>
       <c r="V5" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="W5" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="X5" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="Y5" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
     </row>
     <row r="6">
@@ -4605,76 +4605,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>259.0029130987097</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C6" t="n">
-        <v>259.0029130987097</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="D6" t="n">
-        <v>259.0029130987097</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E6" t="n">
-        <v>259.0029130987097</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F6" t="n">
-        <v>259.0029130987097</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G6" t="n">
-        <v>223.7028973880499</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H6" t="n">
-        <v>110.3337617956292</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I6" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J6" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K6" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L6" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M6" t="n">
-        <v>613.1906659261865</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N6" t="n">
-        <v>851.7806659261865</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="O6" t="n">
-        <v>894.6054414866707</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P6" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R6" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S6" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T6" t="n">
-        <v>487.2265313623206</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U6" t="n">
-        <v>259.0029130987097</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V6" t="n">
-        <v>259.0029130987097</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W6" t="n">
-        <v>259.0029130987097</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X6" t="n">
-        <v>259.0029130987097</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y6" t="n">
-        <v>259.0029130987097</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="7">
@@ -4684,76 +4684,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L7" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M7" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N7" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="8">
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.34998924708335</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C8" t="n">
-        <v>31.34998924708335</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D8" t="n">
-        <v>31.34998924708335</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="E8" t="n">
-        <v>31.34998924708335</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="F8" t="n">
-        <v>31.34998924708335</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="G8" t="n">
-        <v>31.34998924708335</v>
+        <v>487.4018176583718</v>
       </c>
       <c r="H8" t="n">
-        <v>31.34998924708335</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="I8" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K8" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L8" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M8" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N8" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O8" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P8" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q8" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R8" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S8" t="n">
-        <v>591.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T8" t="n">
-        <v>366.0447108019482</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U8" t="n">
-        <v>122.6103673676048</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V8" t="n">
-        <v>31.34998924708335</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W8" t="n">
-        <v>31.34998924708335</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X8" t="n">
-        <v>31.34998924708335</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y8" t="n">
-        <v>31.34998924708335</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>964</v>
+        <v>304.9965798960495</v>
       </c>
       <c r="C9" t="n">
-        <v>817.1401454452562</v>
+        <v>304.9965798960495</v>
       </c>
       <c r="D9" t="n">
-        <v>668.2057357840049</v>
+        <v>304.9965798960495</v>
       </c>
       <c r="E9" t="n">
-        <v>508.9682807785495</v>
+        <v>304.9965798960495</v>
       </c>
       <c r="F9" t="n">
-        <v>362.4337228054344</v>
+        <v>304.9965798960495</v>
       </c>
       <c r="G9" t="n">
-        <v>223.7028973880499</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H9" t="n">
-        <v>110.3337617956292</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I9" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J9" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K9" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L9" t="n">
-        <v>304.1765223866491</v>
+        <v>178.8501590306595</v>
       </c>
       <c r="M9" t="n">
-        <v>542.7665223866492</v>
+        <v>417.4543050195419</v>
       </c>
       <c r="N9" t="n">
-        <v>781.3565223866492</v>
+        <v>656.0584510084244</v>
       </c>
       <c r="O9" t="n">
-        <v>781.3565223866492</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P9" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W9" t="n">
-        <v>964</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X9" t="n">
-        <v>964</v>
+        <v>512.7568786610034</v>
       </c>
       <c r="Y9" t="n">
-        <v>964</v>
+        <v>304.9965798960495</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="C10" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="D10" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="E10" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="F10" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="G10" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="H10" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="I10" t="n">
-        <v>136.0766383258138</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="J10" t="n">
-        <v>41.77443618776046</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="K10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L10" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M10" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N10" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P10" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Q10" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="R10" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="S10" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="T10" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="U10" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="V10" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="W10" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="X10" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="Y10" t="n">
-        <v>153.8122904902707</v>
+        <v>41.77557929797318</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K11" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L11" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M11" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N11" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O11" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P11" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q11" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R11" t="n">
-        <v>802.5254372164702</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S11" t="n">
-        <v>591.3940537960203</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="T11" t="n">
-        <v>366.0447108019482</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="U11" t="n">
-        <v>122.6103673676048</v>
+        <v>122.6530896684844</v>
       </c>
       <c r="V11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C12" t="n">
-        <v>689.4131260035546</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="D12" t="n">
-        <v>668.2057357840049</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E12" t="n">
-        <v>508.9682807785495</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F12" t="n">
-        <v>362.4337228054344</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G12" t="n">
-        <v>223.7028973880499</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H12" t="n">
-        <v>110.3337617956292</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I12" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K12" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L12" t="n">
-        <v>19.28</v>
+        <v>178.8501590306595</v>
       </c>
       <c r="M12" t="n">
-        <v>257.87</v>
+        <v>417.4543050195419</v>
       </c>
       <c r="N12" t="n">
-        <v>496.46</v>
+        <v>656.0584510084244</v>
       </c>
       <c r="O12" t="n">
-        <v>735.0500000000001</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P12" t="n">
-        <v>917.693477613351</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q12" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R12" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S12" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T12" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U12" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V12" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W12" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X12" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y12" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L13" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M13" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N13" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O13" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P13" t="n">
-        <v>151.0633604548096</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Q13" t="n">
-        <v>64.03099353390618</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="R13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>487.3862413384025</v>
+        <v>749.627473042513</v>
       </c>
       <c r="C14" t="n">
-        <v>487.3862413384025</v>
+        <v>749.627473042513</v>
       </c>
       <c r="D14" t="n">
-        <v>487.3862413384025</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E14" t="n">
-        <v>487.3862413384025</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F14" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G14" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H14" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I14" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J14" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K14" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L14" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M14" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N14" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O14" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P14" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q14" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R14" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S14" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T14" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U14" t="n">
-        <v>720.5656565656566</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V14" t="n">
-        <v>487.3862413384025</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W14" t="n">
-        <v>487.3862413384025</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X14" t="n">
-        <v>487.3862413384025</v>
+        <v>749.627473042513</v>
       </c>
       <c r="Y14" t="n">
-        <v>487.3862413384025</v>
+        <v>749.627473042513</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>817.1401454452562</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C15" t="n">
-        <v>817.1401454452562</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="D15" t="n">
-        <v>668.2057357840049</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E15" t="n">
-        <v>508.9682807785495</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F15" t="n">
-        <v>362.4337228054344</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G15" t="n">
-        <v>223.7028973880499</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H15" t="n">
-        <v>110.3337617956292</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I15" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J15" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K15" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L15" t="n">
-        <v>144.6375600578374</v>
+        <v>178.8501590306595</v>
       </c>
       <c r="M15" t="n">
-        <v>383.2275600578374</v>
+        <v>417.4543050195419</v>
       </c>
       <c r="N15" t="n">
-        <v>621.8175600578375</v>
+        <v>656.0584510084244</v>
       </c>
       <c r="O15" t="n">
-        <v>711.9619638733197</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P15" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U15" t="n">
-        <v>817.1401454452562</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V15" t="n">
-        <v>817.1401454452562</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W15" t="n">
-        <v>817.1401454452562</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X15" t="n">
-        <v>817.1401454452562</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y15" t="n">
-        <v>817.1401454452562</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I16" t="n">
-        <v>136.0766383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J16" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K16" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L16" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M16" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N16" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Q16" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="R16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y16" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31.34998924708335</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C17" t="n">
-        <v>31.34998924708335</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D17" t="n">
-        <v>31.34998924708335</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="E17" t="n">
-        <v>31.34998924708335</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="F17" t="n">
-        <v>31.34998924708335</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="G17" t="n">
-        <v>31.34998924708335</v>
+        <v>487.4018176583718</v>
       </c>
       <c r="H17" t="n">
-        <v>31.34998924708335</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="I17" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J17" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K17" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L17" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M17" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N17" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O17" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P17" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q17" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R17" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S17" t="n">
-        <v>591.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T17" t="n">
-        <v>366.0447108019482</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U17" t="n">
-        <v>122.6103673676048</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V17" t="n">
-        <v>31.34998924708335</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W17" t="n">
-        <v>31.34998924708335</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X17" t="n">
-        <v>31.34998924708335</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y17" t="n">
-        <v>31.34998924708335</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K18" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L18" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M18" t="n">
-        <v>613.1906659261865</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N18" t="n">
-        <v>851.7806659261865</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="O18" t="n">
-        <v>964</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="P18" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q18" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R18" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S18" t="n">
-        <v>689.4131260035546</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T18" t="n">
-        <v>487.2265313623206</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U18" t="n">
-        <v>259.0029130987097</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="V18" t="n">
-        <v>23.85080486696694</v>
+        <v>23.90796037760316</v>
       </c>
       <c r="W18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y18" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L19" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M19" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N19" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S19" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T19" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U19" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V19" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>477.1313131313132</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="C20" t="n">
-        <v>233.6969696969697</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="D20" t="n">
-        <v>233.6969696969697</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="E20" t="n">
-        <v>233.6969696969697</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="F20" t="n">
-        <v>233.6969696969697</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="G20" t="n">
-        <v>233.6969696969697</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="H20" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R20" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S20" t="n">
-        <v>964</v>
+        <v>761.6974622895962</v>
       </c>
       <c r="T20" t="n">
-        <v>964</v>
+        <v>761.6974622895962</v>
       </c>
       <c r="U20" t="n">
-        <v>964</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="V20" t="n">
-        <v>964</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="W20" t="n">
-        <v>720.5656565656566</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="X20" t="n">
-        <v>477.1313131313132</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="Y20" t="n">
-        <v>477.1313131313132</v>
+        <v>274.7999090013961</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>533.5897870951551</v>
+        <v>787.171420448546</v>
       </c>
       <c r="C21" t="n">
-        <v>533.5897870951551</v>
+        <v>612.718391167419</v>
       </c>
       <c r="D21" t="n">
-        <v>384.6553774339038</v>
+        <v>463.7839815061678</v>
       </c>
       <c r="E21" t="n">
-        <v>225.4179224284483</v>
+        <v>304.5465265007123</v>
       </c>
       <c r="F21" t="n">
-        <v>78.88336445533329</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="G21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L21" t="n">
-        <v>249.2431058683491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M21" t="n">
-        <v>487.8331058683492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="N21" t="n">
-        <v>542.7665223866492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O21" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P21" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>955.386757468614</v>
       </c>
       <c r="S21" t="n">
-        <v>964</v>
+        <v>955.386757468614</v>
       </c>
       <c r="T21" t="n">
-        <v>761.813405358766</v>
+        <v>955.386757468614</v>
       </c>
       <c r="U21" t="n">
-        <v>533.5897870951551</v>
+        <v>955.386757468614</v>
       </c>
       <c r="V21" t="n">
-        <v>533.5897870951551</v>
+        <v>955.386757468614</v>
       </c>
       <c r="W21" t="n">
-        <v>533.5897870951551</v>
+        <v>955.386757468614</v>
       </c>
       <c r="X21" t="n">
-        <v>533.5897870951551</v>
+        <v>955.386757468614</v>
       </c>
       <c r="Y21" t="n">
-        <v>533.5897870951551</v>
+        <v>955.386757468614</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R22" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S22" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T22" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U22" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V22" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W22" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X22" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y22" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>477.1313131313132</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="C23" t="n">
-        <v>477.1313131313132</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="D23" t="n">
-        <v>477.1313131313132</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="E23" t="n">
-        <v>477.1313131313132</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="F23" t="n">
-        <v>233.6969696969697</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="G23" t="n">
-        <v>233.6969696969697</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="H23" t="n">
-        <v>231.8819086569757</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y23" t="n">
-        <v>720.5656565656566</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>193.733029281127</v>
+        <v>271.3811041200179</v>
       </c>
       <c r="C24" t="n">
-        <v>19.28</v>
+        <v>271.3811041200179</v>
       </c>
       <c r="D24" t="n">
-        <v>19.28</v>
+        <v>271.3811041200179</v>
       </c>
       <c r="E24" t="n">
-        <v>19.28</v>
+        <v>271.3811041200179</v>
       </c>
       <c r="F24" t="n">
-        <v>19.28</v>
+        <v>271.3811041200179</v>
       </c>
       <c r="G24" t="n">
-        <v>19.28</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="H24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L24" t="n">
-        <v>249.2431058683491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M24" t="n">
-        <v>304.1765223866491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="N24" t="n">
-        <v>542.7665223866492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O24" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P24" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>964</v>
+        <v>950.8137977926829</v>
       </c>
       <c r="S24" t="n">
-        <v>964</v>
+        <v>950.8137977926829</v>
       </c>
       <c r="T24" t="n">
-        <v>852.7791716859572</v>
+        <v>950.8137977926829</v>
       </c>
       <c r="U24" t="n">
-        <v>852.7791716859572</v>
+        <v>722.5901795290719</v>
       </c>
       <c r="V24" t="n">
-        <v>852.7791716859572</v>
+        <v>722.5901795290719</v>
       </c>
       <c r="W24" t="n">
-        <v>609.3448282516138</v>
+        <v>479.1414028849718</v>
       </c>
       <c r="X24" t="n">
-        <v>401.4933280460809</v>
+        <v>479.1414028849718</v>
       </c>
       <c r="Y24" t="n">
-        <v>193.733029281127</v>
+        <v>271.3811041200179</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C25" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D25" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>262.7143434343434</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="C26" t="n">
-        <v>262.7143434343434</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="D26" t="n">
-        <v>262.7143434343434</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="E26" t="n">
-        <v>19.28</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="F26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R26" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S26" t="n">
-        <v>731.498029862759</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T26" t="n">
-        <v>506.1486868686869</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U26" t="n">
-        <v>262.7143434343434</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V26" t="n">
-        <v>262.7143434343434</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W26" t="n">
-        <v>262.7143434343434</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X26" t="n">
-        <v>262.7143434343434</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y26" t="n">
-        <v>262.7143434343434</v>
+        <v>477.1596022224361</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>69.80174936342718</v>
+        <v>168.215552771464</v>
       </c>
       <c r="C27" t="n">
-        <v>69.80174936342718</v>
+        <v>168.215552771464</v>
       </c>
       <c r="D27" t="n">
-        <v>69.80174936342718</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E27" t="n">
-        <v>69.80174936342718</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F27" t="n">
-        <v>69.80174936342718</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G27" t="n">
-        <v>69.80174936342718</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H27" t="n">
-        <v>69.80174936342718</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L27" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M27" t="n">
-        <v>374.6006659261865</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N27" t="n">
-        <v>473.3719638733197</v>
+        <v>726.4525409563269</v>
       </c>
       <c r="O27" t="n">
-        <v>711.9619638733197</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P27" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T27" t="n">
-        <v>964</v>
+        <v>772.4148068200968</v>
       </c>
       <c r="U27" t="n">
-        <v>964</v>
+        <v>544.1911885564859</v>
       </c>
       <c r="V27" t="n">
-        <v>728.8478917682573</v>
+        <v>544.1911885564859</v>
       </c>
       <c r="W27" t="n">
-        <v>485.4135483339139</v>
+        <v>544.1911885564859</v>
       </c>
       <c r="X27" t="n">
-        <v>277.5620481283811</v>
+        <v>544.1911885564859</v>
       </c>
       <c r="Y27" t="n">
-        <v>69.80174936342718</v>
+        <v>336.430889791532</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C28" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D28" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="E28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L28" t="n">
-        <v>46.59412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M28" t="n">
-        <v>85.78216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N28" t="n">
-        <v>129.4730138553714</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W28" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X28" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y28" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>40.65058671683502</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C29" t="n">
-        <v>40.65058671683502</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D29" t="n">
-        <v>40.65058671683502</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E29" t="n">
-        <v>40.65058671683502</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="F29" t="n">
-        <v>40.65058671683502</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G29" t="n">
-        <v>40.65058671683502</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H29" t="n">
-        <v>40.65058671683502</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964.0000000000439</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>964.0000000000439</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R29" t="n">
-        <v>964.0000000000439</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S29" t="n">
-        <v>752.868616579594</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T29" t="n">
-        <v>527.5192735855219</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U29" t="n">
-        <v>284.0849301511785</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V29" t="n">
-        <v>40.65058671683502</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W29" t="n">
-        <v>40.65058671683502</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X29" t="n">
-        <v>40.65058671683502</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y29" t="n">
-        <v>40.65058671683502</v>
+        <v>720.6083788665362</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>69.80174936342718</v>
+        <v>76.77296163243852</v>
       </c>
       <c r="C30" t="n">
-        <v>69.80174936342718</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I30" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L30" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M30" t="n">
-        <v>613.1906659261865</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="N30" t="n">
-        <v>851.7806659261865</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O30" t="n">
-        <v>894.6054414866707</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P30" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U30" t="n">
-        <v>964</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="V30" t="n">
-        <v>728.8478917682573</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="W30" t="n">
-        <v>485.4135483339139</v>
+        <v>492.3847606029253</v>
       </c>
       <c r="X30" t="n">
-        <v>277.5620481283811</v>
+        <v>284.5332603973924</v>
       </c>
       <c r="Y30" t="n">
-        <v>69.80174936342718</v>
+        <v>76.77296163243852</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="E31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="F31" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G31" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H31" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I31" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J31" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K31" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L31" t="n">
-        <v>46.59412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M31" t="n">
-        <v>85.78216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N31" t="n">
-        <v>129.4730138553714</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y31" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>19.28</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C32" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D32" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E32" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F32" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K32" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L32" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M32" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N32" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O32" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P32" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q32" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R32" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S32" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T32" t="n">
-        <v>728.5590416377008</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U32" t="n">
-        <v>728.5590416377008</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V32" t="n">
-        <v>728.5590416377008</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W32" t="n">
-        <v>485.1246982033574</v>
+        <v>710.516763498309</v>
       </c>
       <c r="X32" t="n">
-        <v>241.690354769014</v>
+        <v>710.516763498309</v>
       </c>
       <c r="Y32" t="n">
-        <v>19.28</v>
+        <v>710.516763498309</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>720.5656565656566</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C33" t="n">
-        <v>720.5656565656566</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D33" t="n">
-        <v>668.2057357840049</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E33" t="n">
-        <v>508.9682807785495</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F33" t="n">
-        <v>362.4337228054344</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G33" t="n">
-        <v>223.7028973880499</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H33" t="n">
-        <v>110.3337617956292</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I33" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K33" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L33" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M33" t="n">
-        <v>542.7665223866492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N33" t="n">
-        <v>542.7665223866492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O33" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P33" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q33" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R33" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S33" t="n">
-        <v>964</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T33" t="n">
-        <v>964</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="U33" t="n">
-        <v>964</v>
+        <v>562.4161926976942</v>
       </c>
       <c r="V33" t="n">
-        <v>964</v>
+        <v>562.4161926976942</v>
       </c>
       <c r="W33" t="n">
-        <v>720.5656565656566</v>
+        <v>318.9674160535941</v>
       </c>
       <c r="X33" t="n">
-        <v>720.5656565656566</v>
+        <v>318.9674160535941</v>
       </c>
       <c r="Y33" t="n">
-        <v>720.5656565656566</v>
+        <v>111.2071172886402</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C34" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D34" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="E34" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F34" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G34" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H34" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I34" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J34" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K34" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L34" t="n">
-        <v>46.59412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M34" t="n">
-        <v>85.78216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N34" t="n">
-        <v>129.4730138553714</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O34" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P34" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q34" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R34" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S34" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T34" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U34" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V34" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W34" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X34" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y34" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>274.7843326814268</v>
+        <v>749.627473042513</v>
       </c>
       <c r="C35" t="n">
-        <v>274.7843326814268</v>
+        <v>749.627473042513</v>
       </c>
       <c r="D35" t="n">
-        <v>274.7843326814268</v>
+        <v>749.627473042513</v>
       </c>
       <c r="E35" t="n">
-        <v>274.7843326814268</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="F35" t="n">
-        <v>274.7843326814268</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G35" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H35" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I35" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K35" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L35" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M35" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N35" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O35" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P35" t="n">
-        <v>964.000000000073</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q35" t="n">
-        <v>964.000000000073</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R35" t="n">
-        <v>964.000000000073</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S35" t="n">
-        <v>752.8686165796231</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T35" t="n">
-        <v>527.519273585551</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U35" t="n">
-        <v>284.0849301512076</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V35" t="n">
-        <v>274.7843326814268</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W35" t="n">
-        <v>274.7843326814268</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="X35" t="n">
-        <v>274.7843326814268</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="Y35" t="n">
-        <v>274.7843326814268</v>
+        <v>749.627473042513</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>790.5826554506689</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C36" t="n">
-        <v>616.1296261695419</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D36" t="n">
-        <v>508.2141481257637</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E36" t="n">
-        <v>508.2141481257637</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F36" t="n">
-        <v>361.6795901526487</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G36" t="n">
-        <v>222.9487647352642</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H36" t="n">
-        <v>109.5796291428435</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K36" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L36" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M36" t="n">
-        <v>487.8331058683492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N36" t="n">
-        <v>487.8331058683492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O36" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P36" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R36" t="n">
-        <v>964</v>
+        <v>933.9571464551993</v>
       </c>
       <c r="S36" t="n">
-        <v>790.5826554506689</v>
+        <v>933.9571464551993</v>
       </c>
       <c r="T36" t="n">
-        <v>790.5826554506689</v>
+        <v>933.9571464551993</v>
       </c>
       <c r="U36" t="n">
-        <v>790.5826554506689</v>
+        <v>705.7335281915883</v>
       </c>
       <c r="V36" t="n">
-        <v>790.5826554506689</v>
+        <v>470.5814199598456</v>
       </c>
       <c r="W36" t="n">
-        <v>790.5826554506689</v>
+        <v>227.1326433157456</v>
       </c>
       <c r="X36" t="n">
-        <v>790.5826554506689</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y36" t="n">
-        <v>790.5826554506689</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C37" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D37" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="E37" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="F37" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="G37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L37" t="n">
-        <v>46.59412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M37" t="n">
-        <v>85.78216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N37" t="n">
-        <v>129.4730138553714</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O37" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P37" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q37" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R37" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S37" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T37" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U37" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V37" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W37" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X37" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y37" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>243.9518979040591</v>
+        <v>710.516763498309</v>
       </c>
       <c r="C38" t="n">
-        <v>243.9518979040591</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D38" t="n">
-        <v>243.9518979040591</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E38" t="n">
-        <v>243.9518979040591</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F38" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G38" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H38" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I38" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K38" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L38" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M38" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N38" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O38" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P38" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q38" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R38" t="n">
-        <v>802.5254372164702</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S38" t="n">
-        <v>591.3940537960203</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T38" t="n">
-        <v>366.0447108019482</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U38" t="n">
-        <v>243.9518979040591</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V38" t="n">
-        <v>243.9518979040591</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W38" t="n">
-        <v>243.9518979040591</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="X38" t="n">
-        <v>243.9518979040591</v>
+        <v>710.516763498309</v>
       </c>
       <c r="Y38" t="n">
-        <v>243.9518979040591</v>
+        <v>710.516763498309</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>20.03413265278571</v>
+        <v>485.4562706347935</v>
       </c>
       <c r="C39" t="n">
-        <v>20.03413265278571</v>
+        <v>311.0032413536665</v>
       </c>
       <c r="D39" t="n">
-        <v>20.03413265278571</v>
+        <v>162.0688316924152</v>
       </c>
       <c r="E39" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F39" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G39" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H39" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I39" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K39" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L39" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M39" t="n">
-        <v>374.6006659261865</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="N39" t="n">
-        <v>613.1906659261865</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O39" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P39" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S39" t="n">
-        <v>866.0561445281173</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T39" t="n">
-        <v>663.8695498868834</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U39" t="n">
-        <v>435.6459316232725</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V39" t="n">
-        <v>435.6459316232725</v>
+        <v>728.9050472788936</v>
       </c>
       <c r="W39" t="n">
-        <v>435.6459316232725</v>
+        <v>485.4562706347935</v>
       </c>
       <c r="X39" t="n">
-        <v>227.7944314177396</v>
+        <v>485.4562706347935</v>
       </c>
       <c r="Y39" t="n">
-        <v>20.03413265278571</v>
+        <v>485.4562706347935</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L40" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M40" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N40" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O40" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P40" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q40" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="R40" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="S40" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T40" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C41" t="n">
-        <v>506.1486868686869</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D41" t="n">
-        <v>506.1486868686869</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E41" t="n">
-        <v>506.1486868686869</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F41" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K41" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L41" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M41" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N41" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O41" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P41" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q41" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R41" t="n">
-        <v>802.5254372164702</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S41" t="n">
-        <v>802.5254372164702</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T41" t="n">
-        <v>802.5254372164702</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U41" t="n">
-        <v>802.5254372164702</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V41" t="n">
-        <v>802.5254372164702</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W41" t="n">
-        <v>749.5830303030303</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="X41" t="n">
-        <v>749.5830303030303</v>
+        <v>749.627473042513</v>
       </c>
       <c r="Y41" t="n">
-        <v>506.1486868686869</v>
+        <v>506.1786963984129</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>178.5174550054555</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="C42" t="n">
-        <v>178.5174550054555</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D42" t="n">
-        <v>178.5174550054555</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E42" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F42" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G42" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H42" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I42" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J42" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K42" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L42" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M42" t="n">
-        <v>613.1906659261865</v>
+        <v>417.4543050195419</v>
       </c>
       <c r="N42" t="n">
-        <v>781.3565223866492</v>
+        <v>656.0584510084244</v>
       </c>
       <c r="O42" t="n">
-        <v>781.3565223866492</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P42" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T42" t="n">
-        <v>825.3192436916097</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U42" t="n">
-        <v>825.3192436916097</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="V42" t="n">
-        <v>590.1671354598669</v>
+        <v>500.6814290152826</v>
       </c>
       <c r="W42" t="n">
-        <v>346.7327920255235</v>
+        <v>257.2326523711826</v>
       </c>
       <c r="X42" t="n">
-        <v>346.7327920255235</v>
+        <v>49.38115216564972</v>
       </c>
       <c r="Y42" t="n">
-        <v>346.7327920255235</v>
+        <v>20.03527576299844</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L43" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M43" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N43" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T43" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="44">
@@ -7607,76 +7607,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>953.9083846317729</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C44" t="n">
-        <v>953.9083846317729</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D44" t="n">
-        <v>953.9083846317729</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E44" t="n">
-        <v>710.4740411974295</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F44" t="n">
-        <v>467.0396977630861</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G44" t="n">
-        <v>223.6053543287427</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H44" t="n">
-        <v>223.6053543287427</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K44" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L44" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M44" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N44" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O44" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P44" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q44" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R44" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S44" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T44" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U44" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V44" t="n">
-        <v>953.9083846317729</v>
+        <v>710.516763498309</v>
       </c>
       <c r="W44" t="n">
-        <v>953.9083846317729</v>
+        <v>467.067986854209</v>
       </c>
       <c r="X44" t="n">
-        <v>953.9083846317729</v>
+        <v>223.6192102101089</v>
       </c>
       <c r="Y44" t="n">
-        <v>953.9083846317729</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="45">
@@ -7686,76 +7686,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>182.0574242455656</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C45" t="n">
-        <v>182.0574242455656</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D45" t="n">
-        <v>182.0574242455656</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E45" t="n">
-        <v>182.0574242455656</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F45" t="n">
-        <v>35.52286627245059</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G45" t="n">
-        <v>35.52286627245059</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H45" t="n">
-        <v>35.52286627245059</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I45" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J45" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K45" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L45" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M45" t="n">
-        <v>613.1906659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="N45" t="n">
-        <v>851.7806659261865</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="O45" t="n">
-        <v>964</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P45" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q45" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R45" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S45" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T45" t="n">
-        <v>660.6438759116518</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U45" t="n">
-        <v>660.6438759116518</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="V45" t="n">
-        <v>425.4917676799091</v>
+        <v>500.6814290152826</v>
       </c>
       <c r="W45" t="n">
-        <v>182.0574242455656</v>
+        <v>257.2326523711826</v>
       </c>
       <c r="X45" t="n">
-        <v>182.0574242455656</v>
+        <v>49.38115216564972</v>
       </c>
       <c r="Y45" t="n">
-        <v>182.0574242455656</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="46">
@@ -7765,76 +7765,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L46" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M46" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N46" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U46" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
   </sheetData>
@@ -7959,7 +7959,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K2" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L2" t="n">
         <v>417.6612145504504</v>
@@ -8041,19 +8041,19 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L3" t="n">
-        <v>229.6093331288462</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M3" t="n">
-        <v>142.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N3" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O3" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P3" t="n">
-        <v>318.4627686399372</v>
+        <v>177.2597568922521</v>
       </c>
       <c r="Q3" t="n">
         <v>210.0772877358491</v>
@@ -8196,7 +8196,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K5" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L5" t="n">
         <v>417.6612145504504</v>
@@ -8281,19 +8281,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M6" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N6" t="n">
-        <v>372.3417120833333</v>
+        <v>301.2485028631349</v>
       </c>
       <c r="O6" t="n">
-        <v>185.8535934954385</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P6" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q6" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R6" t="n">
         <v>45.52166981132082</v>
@@ -8448,7 +8448,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P8" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q8" t="n">
         <v>212.3149906599047</v>
@@ -8512,25 +8512,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K9" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L9" t="n">
-        <v>299.7048467786739</v>
+        <v>299.7352039419416</v>
       </c>
       <c r="M9" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N9" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O9" t="n">
-        <v>142.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P9" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q9" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8670,7 +8670,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L11" t="n">
         <v>417.6612145504504</v>
@@ -8749,25 +8749,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K12" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L12" t="n">
-        <v>138.5543797798742</v>
+        <v>173.111405903722</v>
       </c>
       <c r="M12" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N12" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O12" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P12" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q12" t="n">
-        <v>186.7560391230408</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8907,7 +8907,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L14" t="n">
         <v>417.6612145504504</v>
@@ -8989,19 +8989,19 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L15" t="n">
-        <v>138.5543797798742</v>
+        <v>173.111405903722</v>
       </c>
       <c r="M15" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N15" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O15" t="n">
-        <v>233.6511977934165</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P15" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q15" t="n">
         <v>210.0772877358491</v>
@@ -9144,7 +9144,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L17" t="n">
         <v>417.6612145504504</v>
@@ -9229,19 +9229,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M18" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N18" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O18" t="n">
-        <v>255.9491071452661</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P18" t="n">
-        <v>133.9744074143302</v>
+        <v>177.2597568922521</v>
       </c>
       <c r="Q18" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9381,7 +9381,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L20" t="n">
         <v>417.6612145504504</v>
@@ -9466,19 +9466,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M21" t="n">
-        <v>383.1340339220183</v>
+        <v>368.5691090902119</v>
       </c>
       <c r="N21" t="n">
-        <v>186.8300115967677</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O21" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P21" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q21" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9703,19 +9703,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M24" t="n">
-        <v>197.6223334354527</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N24" t="n">
-        <v>372.3417120833333</v>
+        <v>357.7767872515269</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P24" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q24" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9855,7 +9855,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L26" t="n">
         <v>417.6612145504504</v>
@@ -9934,25 +9934,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L27" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M27" t="n">
-        <v>142.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N27" t="n">
-        <v>231.1106999087204</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O27" t="n">
-        <v>383.5962444444444</v>
+        <v>382.6009056104135</v>
       </c>
       <c r="P27" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q27" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10107,7 +10107,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P29" t="n">
-        <v>321.742129989281</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q29" t="n">
         <v>212.3149906599047</v>
@@ -10177,16 +10177,16 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M30" t="n">
-        <v>383.1340339220183</v>
+        <v>241.9453110519923</v>
       </c>
       <c r="N30" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>185.8535934954385</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P30" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q30" t="n">
         <v>210.0772877358491</v>
@@ -10329,7 +10329,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L32" t="n">
         <v>417.6612145504504</v>
@@ -10414,13 +10414,13 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M33" t="n">
-        <v>311.9985353972331</v>
+        <v>312.04082470182</v>
       </c>
       <c r="N33" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P33" t="n">
         <v>318.4627686399372</v>
@@ -10581,7 +10581,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P35" t="n">
-        <v>321.7421299893105</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q35" t="n">
         <v>212.3149906599047</v>
@@ -10645,25 +10645,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L36" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M36" t="n">
-        <v>383.1340339220183</v>
+        <v>312.04082470182</v>
       </c>
       <c r="N36" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
-        <v>368.9890303080512</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P36" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q36" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10815,7 +10815,7 @@
         <v>437.3469244119842</v>
       </c>
       <c r="O38" t="n">
-        <v>380.7436030804994</v>
+        <v>380.8001812627454</v>
       </c>
       <c r="P38" t="n">
         <v>321.7987081714826</v>
@@ -10882,25 +10882,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K39" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L39" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M39" t="n">
-        <v>142.1340339220183</v>
+        <v>368.5691090902119</v>
       </c>
       <c r="N39" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>312.4607459196593</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P39" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q39" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -11040,7 +11040,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L41" t="n">
         <v>417.6612145504504</v>
@@ -11125,19 +11125,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M42" t="n">
-        <v>383.1340339220183</v>
+        <v>185.4193833999402</v>
       </c>
       <c r="N42" t="n">
-        <v>301.2062135585481</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O42" t="n">
-        <v>142.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P42" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q42" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11277,7 +11277,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K44" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L44" t="n">
         <v>417.6612145504504</v>
@@ -11356,25 +11356,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K45" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L45" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M45" t="n">
-        <v>383.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N45" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O45" t="n">
-        <v>255.9491071452661</v>
+        <v>369.031319612638</v>
       </c>
       <c r="P45" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q45" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -22549,31 +22549,31 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S2" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V2" t="n">
-        <v>86.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W2" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X2" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y2" t="n">
-        <v>156.060988220185</v>
+        <v>375.044882499874</v>
       </c>
     </row>
     <row r="3">
@@ -22586,25 +22586,25 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C3" t="n">
-        <v>27.31724297911936</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -22634,19 +22634,19 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S3" t="n">
-        <v>171.6831711038378</v>
+        <v>137.0224969565572</v>
       </c>
       <c r="T3" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X3" t="n">
         <v>205.7729852034775</v>
@@ -22683,13 +22683,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I4" t="n">
-        <v>137.8921792844459</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -22704,13 +22704,13 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>177.2933913771695</v>
+        <v>132.9899077786023</v>
       </c>
       <c r="S4" t="n">
         <v>224.0165980369723</v>
@@ -22765,7 +22765,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J5" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -22798,10 +22798,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>10.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V5" t="n">
-        <v>225.4551947762062</v>
+        <v>237.3633207320585</v>
       </c>
       <c r="W5" t="n">
         <v>349.240968717413</v>
@@ -22823,19 +22823,19 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C6" t="n">
-        <v>172.7084989883157</v>
+        <v>27.26179070270013</v>
       </c>
       <c r="D6" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>102.3965016096575</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -22868,16 +22868,16 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V6" t="n">
         <v>232.8005871494253</v>
@@ -22902,13 +22902,13 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C7" t="n">
-        <v>34.05985351325981</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D7" t="n">
         <v>148.6154730182124</v>
       </c>
       <c r="E7" t="n">
-        <v>146.4339626465692</v>
+        <v>13.24699506120115</v>
       </c>
       <c r="F7" t="n">
         <v>145.4210480229312</v>
@@ -22990,16 +22990,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F8" t="n">
-        <v>406.8760457417114</v>
+        <v>176.0015501456288</v>
       </c>
       <c r="G8" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H8" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I8" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -23023,22 +23023,22 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U8" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V8" t="n">
-        <v>237.4044841308187</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W8" t="n">
         <v>349.240968717413</v>
@@ -23060,19 +23060,19 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C9" t="n">
-        <v>27.31724297911936</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>56.86390315940167</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -23120,13 +23120,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W9" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X9" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -23157,10 +23157,10 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I10" t="n">
-        <v>137.8921792844459</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -23178,13 +23178,13 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>177.2933913771695</v>
+        <v>155.2593996044852</v>
       </c>
       <c r="S10" t="n">
         <v>224.0165980369723</v>
@@ -23272,10 +23272,10 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>10.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V11" t="n">
-        <v>225.4551947762062</v>
+        <v>225.414031377446</v>
       </c>
       <c r="W11" t="n">
         <v>349.240968717413</v>
@@ -23297,10 +23297,10 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C12" t="n">
-        <v>172.7084989883157</v>
+        <v>27.26179070270013</v>
       </c>
       <c r="D12" t="n">
-        <v>126.4497492472846</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -23342,10 +23342,10 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T12" t="n">
         <v>200.1647286948216</v>
@@ -23421,7 +23421,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>132.9899077786024</v>
+        <v>132.9899077786023</v>
       </c>
       <c r="S13" t="n">
         <v>224.0165980369723</v>
@@ -23458,13 +23458,13 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D14" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E14" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F14" t="n">
-        <v>165.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G14" t="n">
         <v>415.302737515135</v>
@@ -23473,10 +23473,10 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -23509,16 +23509,16 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U14" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V14" t="n">
-        <v>96.90463739515337</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W14" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X14" t="n">
-        <v>369.731100678469</v>
+        <v>157.445715035027</v>
       </c>
       <c r="Y14" t="n">
         <v>386.2379386560536</v>
@@ -23534,7 +23534,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C15" t="n">
-        <v>172.7084989883157</v>
+        <v>27.26179070270013</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -23588,7 +23588,7 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U15" t="n">
-        <v>80.55012607177844</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23631,13 +23631,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I16" t="n">
-        <v>137.8921792844459</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -23652,13 +23652,13 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>177.2933913771695</v>
+        <v>132.9899077786023</v>
       </c>
       <c r="S16" t="n">
         <v>224.0165980369723</v>
@@ -23701,16 +23701,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F17" t="n">
-        <v>406.8760457417114</v>
+        <v>176.0015501456288</v>
       </c>
       <c r="G17" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H17" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I17" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23734,22 +23734,22 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U17" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V17" t="n">
-        <v>237.4044841308187</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W17" t="n">
         <v>349.240968717413</v>
@@ -23792,7 +23792,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -23831,7 +23831,7 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>247.9164776688802</v>
+        <v>247.1144340662031</v>
       </c>
       <c r="X18" t="n">
         <v>205.7729852034775</v>
@@ -23898,7 +23898,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S19" t="n">
-        <v>224.0165980369723</v>
+        <v>90.82963045160423</v>
       </c>
       <c r="T19" t="n">
         <v>227.9455894282815</v>
@@ -23910,7 +23910,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W19" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X19" t="n">
         <v>225.7096553890372</v>
@@ -23929,10 +23929,10 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C20" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D20" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E20" t="n">
         <v>381.9303700722618</v>
@@ -23944,13 +23944,13 @@
         <v>415.302737515135</v>
       </c>
       <c r="H20" t="n">
-        <v>127.2020021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I20" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J20" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -23971,31 +23971,31 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S20" t="n">
-        <v>209.0200695862453</v>
+        <v>18.67467251196047</v>
       </c>
       <c r="T20" t="n">
         <v>223.0958495641314</v>
       </c>
       <c r="U20" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X20" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y20" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="21">
@@ -24005,10 +24005,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -24020,7 +24020,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>78.33618635243067</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>112.2354442364965</v>
@@ -24053,16 +24053,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>100.1578341526431</v>
+        <v>91.57414009104109</v>
       </c>
       <c r="S21" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24084,7 +24084,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>179.8319801819373</v>
+        <v>46.64501259656927</v>
       </c>
       <c r="C22" t="n">
         <v>167.2468210986278</v>
@@ -24132,7 +24132,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R22" t="n">
-        <v>44.10642379180146</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S22" t="n">
         <v>224.0165980369723</v>
@@ -24163,7 +24163,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>141.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C23" t="n">
         <v>365.2728917710076</v>
@@ -24175,19 +24175,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F23" t="n">
-        <v>165.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G23" t="n">
         <v>415.302737515135</v>
       </c>
       <c r="H23" t="n">
-        <v>337.677891686173</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>10.13979328157632</v>
       </c>
       <c r="J23" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -24232,7 +24232,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y23" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="24">
@@ -24245,7 +24245,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D24" t="n">
         <v>147.4450655646388</v>
@@ -24257,10 +24257,10 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>89.39663285141508</v>
@@ -24290,25 +24290,25 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>100.1578341526431</v>
+        <v>87.04691001186931</v>
       </c>
       <c r="S24" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
-        <v>90.05610866391922</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -24321,7 +24321,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>46.64501259656927</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C25" t="n">
         <v>167.2468210986278</v>
@@ -24330,7 +24330,7 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E25" t="n">
-        <v>146.4339626465692</v>
+        <v>13.24699506120115</v>
       </c>
       <c r="F25" t="n">
         <v>145.4210480229312</v>
@@ -24400,7 +24400,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C26" t="n">
         <v>365.2728917710076</v>
@@ -24409,10 +24409,10 @@
         <v>354.683041620683</v>
       </c>
       <c r="E26" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F26" t="n">
-        <v>406.8760457417114</v>
+        <v>194.5906600982693</v>
       </c>
       <c r="G26" t="n">
         <v>415.302737515135</v>
@@ -24445,19 +24445,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S26" t="n">
-        <v>138.7029363060713</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U26" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24466,10 +24466,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X26" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y26" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="27">
@@ -24479,13 +24479,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>172.7084989883157</v>
       </c>
       <c r="D27" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>157.6450804554009</v>
@@ -24500,7 +24500,7 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I27" t="n">
-        <v>39.38010098162217</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J27" t="n">
         <v>0.7465913262578567</v>
@@ -24533,19 +24533,19 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
-        <v>200.1647286948216</v>
+        <v>10.43880349118763</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -24567,7 +24567,7 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E28" t="n">
-        <v>146.4339626465692</v>
+        <v>13.24699506120118</v>
       </c>
       <c r="F28" t="n">
         <v>145.4210480229312</v>
@@ -24621,7 +24621,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W28" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X28" t="n">
         <v>225.7096553890372</v>
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>382.7338416634806</v>
+        <v>170.4484560200385</v>
       </c>
       <c r="C29" t="n">
         <v>365.2728917710076</v>
@@ -24649,16 +24649,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F29" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G29" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H29" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I29" t="n">
-        <v>189.3190087207392</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J29" t="n">
         <v>11.94928935461252</v>
@@ -24688,16 +24688,16 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U29" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V29" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W29" t="n">
         <v>349.240968717413</v>
@@ -24706,7 +24706,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y29" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="30">
@@ -24719,10 +24719,10 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>172.7084989883157</v>
+        <v>116.5381899775701</v>
       </c>
       <c r="D30" t="n">
-        <v>97.42853369484584</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E30" t="n">
         <v>157.6450804554009</v>
@@ -24740,7 +24740,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -24773,13 +24773,13 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -24807,7 +24807,7 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F31" t="n">
-        <v>12.23408043756322</v>
+        <v>12.23408043756325</v>
       </c>
       <c r="G31" t="n">
         <v>167.9909793584588</v>
@@ -24874,10 +24874,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>382.7338416634806</v>
+        <v>180.4391552345834</v>
       </c>
       <c r="C32" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D32" t="n">
         <v>354.683041620683</v>
@@ -24889,7 +24889,7 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H32" t="n">
         <v>339.4748021157671</v>
@@ -24928,7 +24928,7 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U32" t="n">
         <v>251.3456529078365</v>
@@ -24937,13 +24937,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W32" t="n">
-        <v>108.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X32" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y32" t="n">
-        <v>166.0516874347298</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="33">
@@ -24953,31 +24953,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>166.5331836498673</v>
+        <v>75.52646921322412</v>
       </c>
       <c r="C33" t="n">
         <v>172.7084989883157</v>
       </c>
       <c r="D33" t="n">
-        <v>95.60874399080359</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -25004,25 +25004,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W33" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X33" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y33" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -25041,7 +25041,7 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E34" t="n">
-        <v>146.4339626465692</v>
+        <v>13.24699506120118</v>
       </c>
       <c r="F34" t="n">
         <v>145.4210480229312</v>
@@ -25095,7 +25095,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W34" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X34" t="n">
         <v>225.7096553890372</v>
@@ -25120,13 +25120,13 @@
         <v>354.683041620683</v>
       </c>
       <c r="E35" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F35" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G35" t="n">
-        <v>174.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H35" t="n">
         <v>339.4748021157671</v>
@@ -25135,7 +25135,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -25156,22 +25156,22 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U35" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V35" t="n">
-        <v>318.5446669750519</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W35" t="n">
         <v>349.240968717413</v>
@@ -25180,7 +25180,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y35" t="n">
-        <v>386.2379386560536</v>
+        <v>183.9432522271564</v>
       </c>
     </row>
     <row r="36">
@@ -25193,25 +25193,25 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D36" t="n">
-        <v>40.60874230129835</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E36" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J36" t="n">
         <v>0.7465913262578567</v>
@@ -25238,25 +25238,25 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>100.1578341526431</v>
+        <v>70.35882518776062</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X36" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>205.6826957773044</v>
@@ -25284,7 +25284,7 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.9909793584588</v>
+        <v>34.80401177309076</v>
       </c>
       <c r="H37" t="n">
         <v>162.2271725074396</v>
@@ -25335,7 +25335,7 @@
         <v>286.522998336591</v>
       </c>
       <c r="X37" t="n">
-        <v>92.52268780366913</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y37" t="n">
         <v>218.5846533520948</v>
@@ -25351,16 +25351,16 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C38" t="n">
-        <v>365.2728917710076</v>
+        <v>162.9782053421103</v>
       </c>
       <c r="D38" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E38" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F38" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G38" t="n">
         <v>415.302737515135</v>
@@ -25369,10 +25369,10 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -25396,16 +25396,16 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U38" t="n">
-        <v>130.4737681389262</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25414,7 +25414,7 @@
         <v>349.240968717413</v>
       </c>
       <c r="X38" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y38" t="n">
         <v>386.2379386560536</v>
@@ -25430,13 +25430,13 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C39" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>157.6450804554009</v>
+        <v>16.28526875902051</v>
       </c>
       <c r="F39" t="n">
         <v>145.0692123933839</v>
@@ -25451,7 +25451,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -25478,25 +25478,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>74.71875418667398</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V39" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="40">
@@ -25551,19 +25551,19 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q40" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>177.2933913771695</v>
       </c>
       <c r="S40" t="n">
-        <v>224.0165980369723</v>
+        <v>176.9916737032986</v>
       </c>
       <c r="T40" t="n">
         <v>227.9455894282815</v>
       </c>
       <c r="U40" t="n">
-        <v>153.1320617711229</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25585,10 +25585,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C41" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D41" t="n">
         <v>354.683041620683</v>
@@ -25597,10 +25597,10 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F41" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H41" t="n">
         <v>339.4748021157671</v>
@@ -25633,7 +25633,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S41" t="n">
         <v>209.0200695862453</v>
@@ -25648,13 +25648,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W41" t="n">
-        <v>296.8279858731075</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X41" t="n">
-        <v>369.731100678469</v>
+        <v>167.4364142495718</v>
       </c>
       <c r="Y41" t="n">
-        <v>145.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="42">
@@ -25664,7 +25664,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C42" t="n">
         <v>172.7084989883157</v>
@@ -25673,7 +25673,7 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F42" t="n">
         <v>145.0692123933839</v>
@@ -25688,7 +25688,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -25718,22 +25718,22 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T42" t="n">
-        <v>62.8707799495152</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X42" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>205.6826957773044</v>
+        <v>176.6302781386796</v>
       </c>
     </row>
     <row r="43">
@@ -25797,10 +25797,10 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T43" t="n">
-        <v>94.75862184291347</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U43" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25831,19 +25831,19 @@
         <v>354.683041620683</v>
       </c>
       <c r="E44" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F44" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H44" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I44" t="n">
-        <v>8.193788784950669</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J44" t="n">
         <v>11.94928935461252</v>
@@ -25882,16 +25882,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V44" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W44" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X44" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y44" t="n">
-        <v>386.2379386560536</v>
+        <v>183.9432522271564</v>
       </c>
     </row>
     <row r="45">
@@ -25913,7 +25913,7 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
         <v>137.3435171632106</v>
@@ -25922,10 +25922,10 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I45" t="n">
-        <v>74.06278656794686</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -25949,28 +25949,28 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S45" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U45" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X45" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>205.6826957773044</v>
+        <v>175.8836868124217</v>
       </c>
     </row>
     <row r="46">
@@ -26037,10 +26037,10 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U46" t="n">
-        <v>153.1320617711229</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V46" t="n">
-        <v>252.137643323828</v>
+        <v>118.95067573846</v>
       </c>
       <c r="W46" t="n">
         <v>286.522998336591</v>
@@ -26078,7 +26078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>481856.1408331657</v>
+        <v>481865.9503408642</v>
       </c>
     </row>
     <row r="3">
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>481856.1408331656</v>
+        <v>481865.9503408642</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>481856.1408331657</v>
+        <v>481865.9503408644</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>481856.1408331657</v>
+        <v>481865.9503408642</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>481856.1408331656</v>
+        <v>481865.9503408644</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>481856.1408331656</v>
+        <v>481865.9503408642</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>481856.1408331658</v>
+        <v>481865.9503408642</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>481856.1408331657</v>
+        <v>481865.9503408642</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>481856.1408331657</v>
+        <v>481865.9503408642</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>481856.1408331706</v>
+        <v>481865.9503408642</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>481856.1408331657</v>
+        <v>481865.9503408644</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>481856.1408331741</v>
+        <v>481865.9503408641</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>481856.1408331657</v>
+        <v>481865.9503408644</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>481856.1408331657</v>
+        <v>481865.9503408642</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>481856.1408331657</v>
+        <v>481865.9503408641</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>99694.3739654824</v>
+        <v>99696.4035187994</v>
       </c>
       <c r="C2" t="n">
-        <v>99694.37396548243</v>
+        <v>99696.40351879937</v>
       </c>
       <c r="D2" t="n">
-        <v>99694.37396548243</v>
+        <v>99696.40351879942</v>
       </c>
       <c r="E2" t="n">
-        <v>99694.37396548246</v>
+        <v>99696.40351879939</v>
       </c>
       <c r="F2" t="n">
-        <v>99694.37396548245</v>
+        <v>99696.40351879939</v>
       </c>
       <c r="G2" t="n">
-        <v>99694.37396548249</v>
+        <v>99696.4035187994</v>
       </c>
       <c r="H2" t="n">
-        <v>99694.37396548245</v>
+        <v>99696.40351879937</v>
       </c>
       <c r="I2" t="n">
-        <v>99694.37396548245</v>
+        <v>99696.40351879933</v>
       </c>
       <c r="J2" t="n">
-        <v>99694.37396548243</v>
+        <v>99696.40351879939</v>
       </c>
       <c r="K2" t="n">
-        <v>99694.37396548351</v>
+        <v>99696.40351879936</v>
       </c>
       <c r="L2" t="n">
-        <v>99694.37396548246</v>
+        <v>99696.40351879934</v>
       </c>
       <c r="M2" t="n">
-        <v>99694.37396548413</v>
+        <v>99696.40351879936</v>
       </c>
       <c r="N2" t="n">
-        <v>99694.37396548247</v>
+        <v>99696.40351879931</v>
       </c>
       <c r="O2" t="n">
-        <v>99694.37396548247</v>
+        <v>99696.40351879939</v>
       </c>
       <c r="P2" t="n">
-        <v>99694.37396548247</v>
+        <v>99696.40351879936</v>
       </c>
     </row>
     <row r="3">
@@ -26313,7 +26313,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80764.643</v>
+        <v>80769.43153154773</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26337,7 +26337,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>63056.204</v>
+        <v>63059.94259910623</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="C4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="D4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="E4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="F4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="G4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="H4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="I4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="J4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="K4" t="n">
-        <v>179.5221438966211</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="L4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="M4" t="n">
-        <v>179.5221438966247</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="N4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="O4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="P4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
     </row>
     <row r="5">
@@ -26417,49 +26417,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="C5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="D5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="E5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="F5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="G5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="M5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="N5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="O5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="P5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-29530.1911784142</v>
+        <v>-29533.82927421396</v>
       </c>
       <c r="C6" t="n">
-        <v>51234.45182158583</v>
+        <v>51235.60225733373</v>
       </c>
       <c r="D6" t="n">
-        <v>51234.45182158583</v>
+        <v>51235.60225733378</v>
       </c>
       <c r="E6" t="n">
-        <v>84862.05182158585</v>
+        <v>84863.20225733375</v>
       </c>
       <c r="F6" t="n">
-        <v>84862.05182158583</v>
+        <v>84863.20225733375</v>
       </c>
       <c r="G6" t="n">
-        <v>84862.05182158588</v>
+        <v>84863.20225733376</v>
       </c>
       <c r="H6" t="n">
-        <v>84862.05182158583</v>
+        <v>84863.20225733373</v>
       </c>
       <c r="I6" t="n">
-        <v>84862.05182158583</v>
+        <v>84863.20225733369</v>
       </c>
       <c r="J6" t="n">
-        <v>21805.84782158582</v>
+        <v>21803.25965822752</v>
       </c>
       <c r="K6" t="n">
-        <v>84862.05182158688</v>
+        <v>84863.20225733372</v>
       </c>
       <c r="L6" t="n">
-        <v>84862.05182158585</v>
+        <v>84863.2022573337</v>
       </c>
       <c r="M6" t="n">
-        <v>84862.05182158751</v>
+        <v>84863.20225733372</v>
       </c>
       <c r="N6" t="n">
-        <v>84862.05182158586</v>
+        <v>84863.20225733367</v>
       </c>
       <c r="O6" t="n">
-        <v>84862.05182158586</v>
+        <v>84863.20225733375</v>
       </c>
       <c r="P6" t="n">
-        <v>84862.05182158586</v>
+        <v>84863.20225733372</v>
       </c>
     </row>
   </sheetData>
@@ -26727,49 +26727,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="M4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
   </sheetData>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26895,46 +26895,46 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,49 +26944,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27185,7 +27185,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34614,7 +34614,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L2" t="n">
         <v>181.8947995804632</v>
@@ -34696,19 +34696,19 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L3" t="n">
-        <v>91.05495334897203</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N3" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P3" t="n">
-        <v>184.4883612256069</v>
+        <v>43.28534947792182</v>
       </c>
       <c r="Q3" t="n">
         <v>70.09551364982758</v>
@@ -34851,7 +34851,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L5" t="n">
         <v>181.8947995804632</v>
@@ -34936,19 +34936,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M6" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N6" t="n">
-        <v>241</v>
+        <v>169.9067907798016</v>
       </c>
       <c r="O6" t="n">
-        <v>43.25734905099405</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q6" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -35094,7 +35094,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M8" t="n">
-        <v>219.1673002655598</v>
+        <v>219.1673002655597</v>
       </c>
       <c r="N8" t="n">
         <v>207.9338608153932</v>
@@ -35103,7 +35103,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P8" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35167,25 +35167,25 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>161.1504669987997</v>
+        <v>161.1808241620674</v>
       </c>
       <c r="M9" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N9" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P9" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -35325,7 +35325,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L11" t="n">
         <v>181.8947995804632</v>
@@ -35404,25 +35404,25 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>34.55702612384782</v>
       </c>
       <c r="M12" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N12" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O12" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P12" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>46.77426503701921</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35562,7 +35562,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L14" t="n">
         <v>181.8947995804632</v>
@@ -35644,19 +35644,19 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>34.55702612384782</v>
       </c>
       <c r="M15" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N15" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O15" t="n">
-        <v>91.05495334897201</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P15" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>70.09551364982758</v>
@@ -35799,7 +35799,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L17" t="n">
         <v>181.8947995804632</v>
@@ -35884,19 +35884,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M18" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N18" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O18" t="n">
-        <v>113.3528627008217</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>43.28534947792182</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36036,7 +36036,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L20" t="n">
         <v>181.8947995804632</v>
@@ -36121,19 +36121,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M21" t="n">
-        <v>241</v>
+        <v>226.4350751681936</v>
       </c>
       <c r="N21" t="n">
-        <v>55.48829951343436</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P21" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36358,19 +36358,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M24" t="n">
-        <v>55.48829951343433</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>241</v>
+        <v>226.4350751681936</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P24" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36510,7 +36510,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L26" t="n">
         <v>181.8947995804632</v>
@@ -36589,25 +36589,25 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N27" t="n">
-        <v>99.76898782538704</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O27" t="n">
-        <v>241</v>
+        <v>240.0046611659691</v>
       </c>
       <c r="P27" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36762,7 +36762,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P29" t="n">
-        <v>90.5091342340115</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -36832,16 +36832,16 @@
         <v>232.285965523585</v>
       </c>
       <c r="M30" t="n">
-        <v>241</v>
+        <v>99.81127712997396</v>
       </c>
       <c r="N30" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>43.25734905099405</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q30" t="n">
         <v>70.09551364982758</v>
@@ -36984,7 +36984,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L32" t="n">
         <v>181.8947995804632</v>
@@ -37069,13 +37069,13 @@
         <v>232.285965523585</v>
       </c>
       <c r="M33" t="n">
-        <v>169.8645014752148</v>
+        <v>169.9067907798017</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P33" t="n">
         <v>184.4883612256069</v>
@@ -37233,10 +37233,10 @@
         <v>207.9338608153932</v>
       </c>
       <c r="O35" t="n">
-        <v>150.7019698410586</v>
+        <v>150.7019698410587</v>
       </c>
       <c r="P35" t="n">
-        <v>90.5091342340409</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37300,25 +37300,25 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L36" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M36" t="n">
-        <v>241</v>
+        <v>169.9067907798017</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>226.3927858636067</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P36" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q36" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37470,7 +37470,7 @@
         <v>207.9338608153932</v>
       </c>
       <c r="O38" t="n">
-        <v>150.6453916588127</v>
+        <v>150.7019698410586</v>
       </c>
       <c r="P38" t="n">
         <v>90.5657124162131</v>
@@ -37537,25 +37537,25 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>226.4350751681936</v>
       </c>
       <c r="N39" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>169.8645014752148</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P39" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37695,7 +37695,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L41" t="n">
         <v>181.8947995804632</v>
@@ -37780,19 +37780,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M42" t="n">
-        <v>241</v>
+        <v>43.28534947792188</v>
       </c>
       <c r="N42" t="n">
-        <v>169.8645014752148</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P42" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -37932,7 +37932,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L44" t="n">
         <v>181.8947995804632</v>
@@ -37941,7 +37941,7 @@
         <v>219.1673002655598</v>
       </c>
       <c r="N44" t="n">
-        <v>207.9338608153932</v>
+        <v>207.9338608153933</v>
       </c>
       <c r="O44" t="n">
         <v>150.7019698410586</v>
@@ -38011,25 +38011,25 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M45" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O45" t="n">
-        <v>113.3528627008217</v>
+        <v>226.4350751681936</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
